--- a/artfynd/A 55589-2019 artfynd.xlsx
+++ b/artfynd/A 55589-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55589-2019 artfynd.xlsx
+++ b/artfynd/A 55589-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,6 +1319,113 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125013635</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105676</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vik norrut, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599674</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6280278</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Möckleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Lindeborg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55589-2019 artfynd.xlsx
+++ b/artfynd/A 55589-2019 artfynd.xlsx
@@ -1324,7 +1324,7 @@
         <v>125013635</v>
       </c>
       <c r="B7" t="n">
-        <v>105676</v>
+        <v>105853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Lindeborg</t>
+          <t>Anders Lindeborg, Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55589-2019 artfynd.xlsx
+++ b/artfynd/A 55589-2019 artfynd.xlsx
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Lindeborg, Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Anders Lindeborg, Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 55589-2019 artfynd.xlsx
+++ b/artfynd/A 55589-2019 artfynd.xlsx
@@ -1326,11 +1326,6 @@
       <c r="B7" t="n">
         <v>105853</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>EN</t>
@@ -1421,7 +1416,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Lindeborg, Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Anders Lindeborg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
